--- a/artfynd/A 31621-2024 artfynd.xlsx
+++ b/artfynd/A 31621-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>83338716</v>
       </c>
       <c r="B2" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>427305.1631846389</v>
+        <v>427305</v>
       </c>
       <c r="R2" t="n">
-        <v>6466431.654757794</v>
+        <v>6466432</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -757,19 +752,9 @@
           <t>2007-09-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2007-09-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -803,12 +788,7 @@
         <v>61469054</v>
       </c>
       <c r="B3" t="n">
-        <v>103164</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106140</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -840,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>427282.2130736737</v>
+        <v>427282</v>
       </c>
       <c r="R3" t="n">
-        <v>6466442.582095843</v>
+        <v>6466443</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,19 +853,9 @@
           <t>2016-06-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2016-08-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,12 +890,7 @@
         <v>61469059</v>
       </c>
       <c r="B4" t="n">
-        <v>96879</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99706</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -957,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>427282.2130736737</v>
+        <v>427282</v>
       </c>
       <c r="R4" t="n">
-        <v>6466442.582095843</v>
+        <v>6466443</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,19 +955,9 @@
           <t>2016-06-27</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2016-08-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 31621-2024 artfynd.xlsx
+++ b/artfynd/A 31621-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83338716</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61469054</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,8 +1001,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61469059</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>